--- a/DateBase/orders/Nha Thu_2026-8-25.xlsx
+++ b/DateBase/orders/Nha Thu_2026-8-25.xlsx
@@ -998,6 +998,9 @@
       <c r="G2" t="str">
         <v>0101065551551010795159.51012651284171076861051041081251510555555102030303010105151515101055</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
